--- a/LubanTools/DesignerConfigs/Datas/__enums__.xlsx
+++ b/LubanTools/DesignerConfigs/Datas/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="55">
   <si>
     <t>##var</t>
   </si>
@@ -155,10 +155,43 @@
     <t>航站楼</t>
   </si>
   <si>
+    <t>EngineeringDepartment</t>
+  </si>
+  <si>
+    <t>工程署</t>
+  </si>
+  <si>
+    <t>TalentCenter</t>
+  </si>
+  <si>
+    <t>人才中心</t>
+  </si>
+  <si>
     <t>Shop</t>
   </si>
   <si>
     <t>商店</t>
+  </si>
+  <si>
+    <t>Factory</t>
+  </si>
+  <si>
+    <t>工厂</t>
+  </si>
+  <si>
+    <t>task.TaskType</t>
+  </si>
+  <si>
+    <t>Build</t>
+  </si>
+  <si>
+    <t>建造</t>
+  </si>
+  <si>
+    <t>Collect</t>
+  </si>
+  <si>
+    <t>收集</t>
   </si>
 </sst>
 </file>
@@ -1139,7 +1172,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr defaultColWidth="14.625" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14.625" style="2"/>
@@ -1356,6 +1389,64 @@
         <v>3</v>
       </c>
     </row>
+    <row r="15" customHeight="1" spans="1:12">
+      <c r="H15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J15" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:12">
+      <c r="H16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J16" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="2:10">
+      <c r="H17" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J17" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="2:10">
+      <c r="B18" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="J18" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="2:10">
+      <c r="H19" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J19" s="2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/LubanTools/DesignerConfigs/Datas/__enums__.xlsx
+++ b/LubanTools/DesignerConfigs/Datas/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="65">
   <si>
     <t>##var</t>
   </si>
@@ -192,6 +192,36 @@
   </si>
   <si>
     <t>收集</t>
+  </si>
+  <si>
+    <t>item.ItemType</t>
+  </si>
+  <si>
+    <t>Resource</t>
+  </si>
+  <si>
+    <t>基础资源</t>
+  </si>
+  <si>
+    <t>Consumable</t>
+  </si>
+  <si>
+    <t>消耗品</t>
+  </si>
+  <si>
+    <t>item.ItemQuality</t>
+  </si>
+  <si>
+    <t>Common</t>
+  </si>
+  <si>
+    <t>普通</t>
+  </si>
+  <si>
+    <t>Rare</t>
+  </si>
+  <si>
+    <t>稀有</t>
   </si>
 </sst>
 </file>
@@ -1172,7 +1202,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr defaultColWidth="14.625" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14.625" style="2"/>
@@ -1447,6 +1477,56 @@
         <v>2</v>
       </c>
     </row>
+    <row r="20" customHeight="1" spans="2:10">
+      <c r="B20" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="J20" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="2:10">
+      <c r="H21" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J21" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="2:10">
+      <c r="B27" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J27" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="2:10">
+      <c r="H28" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J28" s="2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
